--- a/output/yearly_surface_area_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_32_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622876187</v>
+        <v>10.84497628608014</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907158142922</v>
+        <v>37.78907178115342</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.009277697694727</v>
+        <v>5.476188694288708</v>
       </c>
       <c r="C2" t="n">
-        <v>7.834346679889546</v>
+        <v>4.661338099763856</v>
       </c>
       <c r="D2" t="n">
-        <v>26.70353755551324</v>
+        <v>17.27090561310989</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11538856521139</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C3" t="n">
-        <v>29.64878066825367</v>
+        <v>18.0052528958865</v>
       </c>
       <c r="D3" t="n">
-        <v>77.22918315457534</v>
+        <v>57.39297079026854</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.58322455624739</v>
+        <v>38.49236398810894</v>
       </c>
       <c r="C4" t="n">
-        <v>64.94948286985624</v>
+        <v>48.71530283243098</v>
       </c>
       <c r="D4" t="n">
-        <v>79.86910273129502</v>
+        <v>78.43967807391167</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.02447124381072</v>
+        <v>49.1119289049467</v>
       </c>
       <c r="C5" t="n">
-        <v>123.822929198129</v>
+        <v>92.84878912914211</v>
       </c>
       <c r="D5" t="n">
-        <v>54.8060655895782</v>
+        <v>63.59270754258716</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="C6" t="n">
-        <v>134.0782657166912</v>
+        <v>92.61906016634835</v>
       </c>
       <c r="D6" t="n">
-        <v>41.37870223859457</v>
+        <v>47.21519234034186</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.40999499194344</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="C7" t="n">
-        <v>114.8625179014683</v>
+        <v>64.25833248606648</v>
       </c>
       <c r="D7" t="n">
-        <v>38.44720359371359</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>16.85660808191773</v>
       </c>
       <c r="C8" t="n">
-        <v>74.01886816168827</v>
+        <v>42.05807164993335</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.697324064439026</v>
+        <v>7.727180127212415</v>
       </c>
       <c r="C21" t="n">
-        <v>94.29221978937807</v>
+        <v>96.58975159015519</v>
       </c>
       <c r="D21" t="n">
-        <v>8.659489572493904</v>
+        <v>8.693077643113966</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.821763886183585</v>
+        <v>8.353691215436109</v>
       </c>
       <c r="C2" t="n">
-        <v>9.92939628075224</v>
+        <v>10.34958429816987</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6874697393468</v>
+        <v>17.67636741496382</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.05434028109884</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C3" t="n">
-        <v>29.89912633283661</v>
+        <v>18.0052528958865</v>
       </c>
       <c r="D3" t="n">
-        <v>79.69336989223484</v>
+        <v>57.61386402372407</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.63878326476196</v>
+        <v>36.65453228575891</v>
       </c>
       <c r="C4" t="n">
-        <v>68.791061636574</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="D4" t="n">
-        <v>97.17535126175778</v>
+        <v>88.27973531357743</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>53.87340527054373</v>
       </c>
       <c r="C5" t="n">
-        <v>121.7367153266045</v>
+        <v>91.32708018755955</v>
       </c>
       <c r="D5" t="n">
-        <v>67.76513528563609</v>
+        <v>75.2755052231242</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.87430490278997</v>
+        <v>56.31206656789281</v>
       </c>
       <c r="C6" t="n">
-        <v>162.5764380755676</v>
+        <v>120.2719477518683</v>
       </c>
       <c r="D6" t="n">
-        <v>48.26173539306896</v>
+        <v>55.8692983532775</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>43.95677170994669</v>
       </c>
       <c r="C7" t="n">
-        <v>152.9504018354276</v>
+        <v>98.15415372289186</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>44.73529763941441</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.02903582496668</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="C8" t="n">
-        <v>110.3189895262141</v>
+        <v>63.83814446864884</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>12.31406145436774</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86600895279948</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
         <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.878213634288198</v>
+        <v>7.921563528361353</v>
       </c>
       <c r="C21" t="n">
-        <v>102.4167772457466</v>
+        <v>105.9509121918331</v>
       </c>
       <c r="D21" t="n">
-        <v>9.847767042860248</v>
+        <v>9.90195441045169</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.937610115284709</v>
+        <v>10.00008211545801</v>
       </c>
       <c r="C2" t="n">
-        <v>16.81341118293087</v>
+        <v>7.845145904636262</v>
       </c>
       <c r="D2" t="n">
-        <v>29.02537087605695</v>
+        <v>15.88860484553038</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38322576202152</v>
+        <v>22.96307880233289</v>
       </c>
       <c r="C3" t="n">
-        <v>34.05682786032185</v>
+        <v>29.09900195387546</v>
       </c>
       <c r="D3" t="n">
-        <v>84.66592201424493</v>
+        <v>57.92311455056181</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.17481751128071</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>70.55231701799278</v>
+        <v>45.11621574866217</v>
       </c>
       <c r="D4" t="n">
-        <v>109.121257327033</v>
+        <v>95.63106212297755</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.20948178056562</v>
+        <v>54.87969666739671</v>
       </c>
       <c r="C5" t="n">
-        <v>122.4730261047896</v>
+        <v>88.33274968960677</v>
       </c>
       <c r="D5" t="n">
-        <v>82.19682653806422</v>
+        <v>86.76195336281188</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.71079500453725</v>
+        <v>63.79887456047898</v>
       </c>
       <c r="C6" t="n">
-        <v>176.3827560403905</v>
+        <v>130.9386365585099</v>
       </c>
       <c r="D6" t="n">
-        <v>56.67433147075987</v>
+        <v>65.48944410719199</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.86074036137975</v>
+        <v>54.61658828265855</v>
       </c>
       <c r="C7" t="n">
-        <v>187.0857695120892</v>
+        <v>133.7268000385708</v>
       </c>
       <c r="D7" t="n">
-        <v>44.37597797966008</v>
+        <v>49.46633982617978</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.87181732356695</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="C8" t="n">
-        <v>149.4563617560132</v>
+        <v>93.87962421860124</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>42.39186586937727</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>18.52656092684155</v>
       </c>
       <c r="C9" t="n">
-        <v>95.51717938928489</v>
+        <v>59.24061996966101</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>53.52488483553611</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>36.66729500591412</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.042746474135212</v>
+        <v>8.102028302240784</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5877640193592</v>
+        <v>114.4411497691511</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05877640193592</v>
+        <v>11.14028891558108</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.571418221600648</v>
+        <v>8.873035750982671</v>
       </c>
       <c r="C2" t="n">
-        <v>11.43245201595411</v>
+        <v>5.083489612589984</v>
       </c>
       <c r="D2" t="n">
-        <v>24.03220205225767</v>
+        <v>12.91685454477528</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.13350199224434</v>
+        <v>26.88025214227767</v>
       </c>
       <c r="C3" t="n">
-        <v>53.98139751801087</v>
+        <v>40.39400929123502</v>
       </c>
       <c r="D3" t="n">
-        <v>90.10480429577225</v>
+        <v>65.16350386938204</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.72214970416493</v>
+        <v>26.36777984066083</v>
       </c>
       <c r="C4" t="n">
-        <v>99.74065801295471</v>
+        <v>70.51402885752717</v>
       </c>
       <c r="D4" t="n">
-        <v>100.7744383455266</v>
+        <v>94.57175635009524</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.00435326364027</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="C5" t="n">
-        <v>105.3906160508951</v>
+        <v>78.22074833586463</v>
       </c>
       <c r="D5" t="n">
-        <v>55.95961914206821</v>
+        <v>64.10812508731674</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.96231803880691</v>
+        <v>33.89189424600839</v>
       </c>
       <c r="C6" t="n">
-        <v>123.210318630679</v>
+        <v>88.07062305257288</v>
       </c>
       <c r="D6" t="n">
-        <v>29.22270216461057</v>
+        <v>32.56358960216246</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="C7" t="n">
-        <v>105.1010004781423</v>
+        <v>65.99504417487908</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>12.85107744859075</v>
       </c>
       <c r="C8" t="n">
-        <v>70.34713174780519</v>
+        <v>43.64359419229195</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.476368620737956</v>
+        <v>5.17086515826795</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7402788267311</v>
+        <v>2.125483779694344</v>
       </c>
       <c r="D2" t="n">
-        <v>16.45998200940202</v>
+        <v>10.03247978969815</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.35792130588936</v>
+        <v>29.68805057642355</v>
       </c>
       <c r="C3" t="n">
-        <v>50.26548245743669</v>
+        <v>29.7960428238907</v>
       </c>
       <c r="D3" t="n">
-        <v>89.86427610823179</v>
+        <v>61.2217868368311</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.54118933141402</v>
+        <v>38.19882142453914</v>
       </c>
       <c r="C4" t="n">
-        <v>119.2420944101133</v>
+        <v>88.98168492211391</v>
       </c>
       <c r="D4" t="n">
-        <v>117.9020087938164</v>
+        <v>105.7263737657475</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.39138284329177</v>
+        <v>39.98167525545136</v>
       </c>
       <c r="C5" t="n">
-        <v>143.9242134425824</v>
+        <v>105.6851403621692</v>
       </c>
       <c r="D5" t="n">
-        <v>72.52661165123313</v>
+        <v>79.20249604011144</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.75226508782709</v>
+        <v>41.05668899160162</v>
       </c>
       <c r="C6" t="n">
-        <v>147.8443320256399</v>
+        <v>108.4379609248772</v>
       </c>
       <c r="D6" t="n">
-        <v>35.70321876034376</v>
+        <v>40.77492740048278</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="C7" t="n">
-        <v>133.966346478407</v>
+        <v>90.24912120829654</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>32.45854259780804</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>93.6292785540183</v>
+        <v>59.33192250615598</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>45.70624611891449</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.000621894805752</v>
+        <v>5.717698629533423</v>
       </c>
       <c r="C2" t="n">
-        <v>10.62251015995049</v>
+        <v>4.934263961544469</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30388412442678</v>
+        <v>9.799805583791661</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57190124768616</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="C3" t="n">
-        <v>35.35273482992764</v>
+        <v>17.5438314748905</v>
       </c>
       <c r="D3" t="n">
-        <v>82.79569263765475</v>
+        <v>55.81726572495241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.51865019194535</v>
+        <v>47.80914970141117</v>
       </c>
       <c r="C4" t="n">
-        <v>122.3561981279842</v>
+        <v>81.89837523597318</v>
       </c>
       <c r="D4" t="n">
-        <v>133.2045102599115</v>
+        <v>111.7376149588507</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.84637399871455</v>
+        <v>48.81740459367266</v>
       </c>
       <c r="C5" t="n">
-        <v>182.4578108342697</v>
+        <v>136.1438628864265</v>
       </c>
       <c r="D5" t="n">
-        <v>94.0023426816321</v>
+        <v>97.04576056479723</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.94472869558847</v>
+        <v>48.26173539306896</v>
       </c>
       <c r="C6" t="n">
-        <v>185.3588753003191</v>
+        <v>139.5122392596973</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21519234034186</v>
+        <v>53.89696721544566</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="C7" t="n">
-        <v>172.2937768522025</v>
+        <v>123.7856227853676</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="C8" t="n">
-        <v>131.8487166803466</v>
+        <v>88.45546815263761</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>75.43749359432489</v>
+        <v>54.80312034646543</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.388592164432489</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C2" t="n">
-        <v>5.067781649322035</v>
+        <v>2.158863201638736</v>
       </c>
       <c r="D2" t="n">
-        <v>11.42656152972863</v>
+        <v>6.728898764907639</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.76334205001429</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="C3" t="n">
-        <v>40.15838984221578</v>
+        <v>19.51714436042659</v>
       </c>
       <c r="D3" t="n">
-        <v>80.80765353655497</v>
+        <v>53.56906348222721</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.84972015245478</v>
+        <v>53.62895009218627</v>
       </c>
       <c r="C4" t="n">
-        <v>121.9095029225519</v>
+        <v>74.81506554983244</v>
       </c>
       <c r="D4" t="n">
-        <v>143.1083811003533</v>
+        <v>117.2255846255904</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14718970684157</v>
+        <v>51.8362787842316</v>
       </c>
       <c r="C5" t="n">
-        <v>220.4759906812275</v>
+        <v>159.9021573291993</v>
       </c>
       <c r="D5" t="n">
-        <v>99.81919782929447</v>
+        <v>106.6914317590221</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.86672865859647</v>
+        <v>42.38499363544755</v>
       </c>
       <c r="C6" t="n">
-        <v>222.5514053280052</v>
+        <v>176.906027566754</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>53.25294072145974</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>177.0847056489269</v>
+        <v>127.1392729430747</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>95.63204387068178</v>
+        <v>69.84644041863932</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.633047342789946</v>
+        <v>4.052654523130833</v>
       </c>
       <c r="C2" t="n">
-        <v>7.289476704032567</v>
+        <v>4.315762907868979</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4658314378985</v>
+        <v>10.66668880664159</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.67436286182632</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="C3" t="n">
-        <v>29.97766614917636</v>
+        <v>13.46466976374501</v>
       </c>
       <c r="D3" t="n">
-        <v>72.92912820997431</v>
+        <v>47.01098881785852</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.62075195318702</v>
+        <v>50.24682925105601</v>
       </c>
       <c r="C4" t="n">
-        <v>111.3036824735736</v>
+        <v>61.72051467058848</v>
       </c>
       <c r="D4" t="n">
-        <v>149.0430459725253</v>
+        <v>117.4680763085394</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.22206457427158</v>
+        <v>65.38439710283758</v>
       </c>
       <c r="C5" t="n">
-        <v>224.157544572153</v>
+        <v>150.4037482906114</v>
       </c>
       <c r="D5" t="n">
-        <v>122.0312396378786</v>
+        <v>123.8474728907351</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>54.90325861229863</v>
       </c>
       <c r="C6" t="n">
-        <v>280.1112732279957</v>
+        <v>215.386610582412</v>
       </c>
       <c r="D6" t="n">
-        <v>61.78629176677302</v>
+        <v>70.03788122096746</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>240.8040586453619</v>
+        <v>188.2236151013112</v>
       </c>
       <c r="D7" t="n">
-        <v>38.44720359371359</v>
+        <v>42.16017341117502</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>150.7080900789279</v>
+        <v>113.2396889463483</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>34.88149593188918</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>62.67968217763759</v>
+        <v>52.58437053486764</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
         <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>22.34752299177014</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.857466656434965</v>
+        <v>2.96095107600838</v>
       </c>
       <c r="C2" t="n">
-        <v>4.811545498513618</v>
+        <v>2.758711048933538</v>
       </c>
       <c r="D2" t="n">
-        <v>9.434595437811847</v>
+        <v>8.071929624317274</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.24591995214721</v>
+        <v>16.25283324380595</v>
       </c>
       <c r="C3" t="n">
-        <v>29.80586030093317</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="D3" t="n">
-        <v>67.78967897824225</v>
+        <v>45.18493808795944</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.11100391050467</v>
+        <v>44.59294422229862</v>
       </c>
       <c r="C4" t="n">
-        <v>99.05147112457344</v>
+        <v>50.41274461307372</v>
       </c>
       <c r="D4" t="n">
-        <v>150.9957421562722</v>
+        <v>115.7068209271206</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.63363784652926</v>
+        <v>72.1339125695344</v>
       </c>
       <c r="C5" t="n">
-        <v>222.4394860897211</v>
+        <v>140.5617275555371</v>
       </c>
       <c r="D5" t="n">
-        <v>138.0337272171016</v>
+        <v>135.1866588747858</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.36361617013237</v>
+        <v>65.81145735418494</v>
       </c>
       <c r="C6" t="n">
-        <v>318.028333061416</v>
+        <v>234.8281603696116</v>
       </c>
       <c r="D6" t="n">
-        <v>72.8554971321558</v>
+        <v>83.32092765942681</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>298.5946372558504</v>
+        <v>237.3306352677367</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>48.08894779712151</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>193.8509929420539</v>
+        <v>151.2922299629547</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>70.9999939711293</v>
+        <v>67.22811929141305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.368957210347553</v>
+        <v>5.307328089158257</v>
       </c>
       <c r="C2" t="n">
-        <v>8.691412425697012</v>
+        <v>4.75853112248429</v>
       </c>
       <c r="D2" t="n">
-        <v>10.38394546781851</v>
+        <v>17.41325903022567</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.899542938997335</v>
+        <v>13.17996292951343</v>
       </c>
       <c r="C3" t="n">
-        <v>24.58296251434013</v>
+        <v>12.91489104936679</v>
       </c>
       <c r="D3" t="n">
-        <v>61.62430339557228</v>
+        <v>41.60155896745859</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.31222113214627</v>
+        <v>37.9690924617454</v>
       </c>
       <c r="C4" t="n">
-        <v>88.0882945112493</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D4" t="n">
-        <v>148.3410963639888</v>
+        <v>112.4523272875424</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.57825906446394</v>
+        <v>71.00490270965058</v>
       </c>
       <c r="C5" t="n">
-        <v>205.2343575727958</v>
+        <v>118.3742294395592</v>
       </c>
       <c r="D5" t="n">
-        <v>154.3061954149925</v>
+        <v>142.3534171157875</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.61520562432682</v>
+        <v>79.09450379264429</v>
       </c>
       <c r="C6" t="n">
-        <v>332.9214457348402</v>
+        <v>230.8432464380738</v>
       </c>
       <c r="D6" t="n">
-        <v>91.0492455872577</v>
+        <v>102.1184509526405</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.30829414132927</v>
+        <v>44.97484407925062</v>
       </c>
       <c r="C7" t="n">
-        <v>364.6495680406885</v>
+        <v>285.6591295046944</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76577287597506</v>
+        <v>57.97023844036566</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>267.7864125488812</v>
+        <v>221.222118936455</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>130.1296764502104</v>
+        <v>114.3765527878661</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>51.10487674456772</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.47420950334699</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>25.23287949455151</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>12.59876828859932</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.98419422574081</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.16791991515521</v>
+        <v>5.292601873594555</v>
       </c>
       <c r="C2" t="n">
-        <v>5.113923791421636</v>
+        <v>2.928553401768235</v>
       </c>
       <c r="D2" t="n">
-        <v>8.275151399096364</v>
+        <v>15.4821612959722</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.731802950291373</v>
+        <v>3.674681656995811</v>
       </c>
       <c r="C2" t="n">
-        <v>5.076617378660257</v>
+        <v>2.587886948394592</v>
       </c>
       <c r="D2" t="n">
-        <v>7.725372684718151</v>
+        <v>12.67632635723482</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.92332586807751</v>
+        <v>18.55503161026472</v>
       </c>
       <c r="C3" t="n">
-        <v>30.86123908299849</v>
+        <v>16.74861583445059</v>
       </c>
       <c r="D3" t="n">
-        <v>66.44468462342412</v>
+        <v>48.6946861306418</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.77765165941726</v>
+        <v>53.09291584566751</v>
       </c>
       <c r="C4" t="n">
-        <v>124.9087421590259</v>
+        <v>64.28582142178539</v>
       </c>
       <c r="D4" t="n">
-        <v>150.2682671074253</v>
+        <v>117.81266975273</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="C5" t="n">
-        <v>293.1498644880976</v>
+        <v>186.8756755033804</v>
       </c>
       <c r="D5" t="n">
-        <v>138.8436690731052</v>
+        <v>135.1130277969673</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.9459471230042</v>
+        <v>27.89439752076462</v>
       </c>
       <c r="C6" t="n">
-        <v>298.9087965212095</v>
+        <v>240.1816306008695</v>
       </c>
       <c r="D6" t="n">
-        <v>72.2114706381699</v>
+        <v>83.84419918579036</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>188.2835017112703</v>
+        <v>155.525526063667</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>95.88238953526472</v>
+        <v>84.28304040958866</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>25.78560345204247</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>10.40652566501619</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.366633862040565</v>
+        <v>7.539822368615503</v>
       </c>
       <c r="C2" t="n">
-        <v>8.477391426171208</v>
+        <v>3.11508546557513</v>
       </c>
       <c r="D2" t="n">
-        <v>10.81591445768711</v>
+        <v>15.81791901082461</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.98084807200057</v>
+        <v>11.24591995214721</v>
       </c>
       <c r="C3" t="n">
-        <v>13.09160563613122</v>
+        <v>7.37783399741478</v>
       </c>
       <c r="D3" t="n">
-        <v>10.08745766113598</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39881693057494</v>
+        <v>13.39793269759716</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14674746006878</v>
+        <v>70.14211824036163</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576331403597051</v>
+        <v>1.576227376187902</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.858268477689965</v>
+        <v>5.084471360294231</v>
       </c>
       <c r="C2" t="n">
-        <v>6.515859513086081</v>
+        <v>3.567671157232909</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0346642692849</v>
+        <v>14.05371838629309</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.56837516749667</v>
+        <v>20.07183181332604</v>
       </c>
       <c r="C3" t="n">
-        <v>25.79542092908494</v>
+        <v>10.41634314205866</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73388961888688</v>
+        <v>25.52544031041707</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.82653375598458</v>
+        <v>13.13283903970958</v>
       </c>
       <c r="C4" t="n">
-        <v>20.81599657314512</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D4" t="n">
-        <v>20.35653864755761</v>
+        <v>23.53445596620454</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44375897917685</v>
+        <v>15.44251875943188</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1599185154077</v>
+        <v>86.15299939472523</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251317679826705</v>
+        <v>3.251056580933028</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.581415625092364</v>
+        <v>5.480115685105695</v>
       </c>
       <c r="C2" t="n">
-        <v>5.083489612589984</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="D2" t="n">
-        <v>15.234760874502</v>
+        <v>13.67967251097506</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.19254572321939</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C3" t="n">
-        <v>25.53034904893831</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="D3" t="n">
-        <v>23.27723806769188</v>
+        <v>30.84651286743478</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.74691438094935</v>
+        <v>27.59300097556086</v>
       </c>
       <c r="C4" t="n">
-        <v>46.57116584635595</v>
+        <v>20.16509784522949</v>
       </c>
       <c r="D4" t="n">
-        <v>24.17259197396497</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.60916660271853</v>
+        <v>11.85460352878024</v>
       </c>
       <c r="C5" t="n">
-        <v>24.17553721707771</v>
+        <v>15.11891464540088</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>31.31775176547326</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74085304651917</v>
+        <v>16.74158726413862</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1192035837669</v>
+        <v>102.1236823112456</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022255913955751</v>
+        <v>5.022476179241587</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.912665512051039</v>
+        <v>5.752059799182062</v>
       </c>
       <c r="C2" t="n">
-        <v>11.02011798017045</v>
+        <v>9.006553438760239</v>
       </c>
       <c r="D2" t="n">
-        <v>19.30312336090079</v>
+        <v>19.99034675387355</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.59229696529709</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C3" t="n">
-        <v>22.12859325372311</v>
+        <v>17.72545480017616</v>
       </c>
       <c r="D3" t="n">
-        <v>29.67823309938108</v>
+        <v>34.3808046027233</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>32.77466535857552</v>
       </c>
       <c r="C4" t="n">
-        <v>56.43674852633215</v>
+        <v>26.50816976236813</v>
       </c>
       <c r="D4" t="n">
-        <v>29.82647700272235</v>
+        <v>38.5817030291954</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.64186737659495</v>
+        <v>26.80171232593793</v>
       </c>
       <c r="C5" t="n">
-        <v>58.1930951692297</v>
+        <v>27.14532402242431</v>
       </c>
       <c r="D5" t="n">
-        <v>31.90680038802134</v>
+        <v>35.44109212330986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>25.88181472705867</v>
+        <v>18.55601335796896</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.94436884268997</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.29864089520282</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>44.07556318216055</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07229373089132</v>
+        <v>18.07829052543728</v>
       </c>
       <c r="C21" t="n">
-        <v>117.900201958672</v>
+        <v>117.9393239040432</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884683326053838</v>
+        <v>6.886967819214202</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.089781009442965</v>
+        <v>6.878124415953153</v>
       </c>
       <c r="C2" t="n">
-        <v>8.382161898859268</v>
+        <v>5.998478472948011</v>
       </c>
       <c r="D2" t="n">
-        <v>35.35666182074463</v>
+        <v>23.23894990722625</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.82300767579509</v>
+        <v>17.3131207643925</v>
       </c>
       <c r="C3" t="n">
-        <v>32.17678100668921</v>
+        <v>26.15375884113503</v>
       </c>
       <c r="D3" t="n">
-        <v>35.50981446260713</v>
+        <v>39.44171401811561</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.53972455762427</v>
+        <v>25.39781310886498</v>
       </c>
       <c r="C4" t="n">
-        <v>46.78813208899449</v>
+        <v>30.54118933141402</v>
       </c>
       <c r="D4" t="n">
-        <v>32.49388551516093</v>
+        <v>40.36848385092459</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.10128424445345</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="C5" t="n">
-        <v>61.99736752318609</v>
+        <v>29.25608158655496</v>
       </c>
       <c r="D5" t="n">
-        <v>28.83883881225006</v>
+        <v>33.57577148524092</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.23650338573225</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C6" t="n">
-        <v>40.85543071223103</v>
+        <v>21.37362926915731</v>
       </c>
       <c r="D6" t="n">
-        <v>30.59125846433062</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>19.10382857693868</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065446806789106</v>
+        <v>7.070967657508074</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23856381364787</v>
+        <v>67.1741927463267</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29908510509183</v>
+        <v>5.303225743131056</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.069745144730529</v>
+        <v>5.292601873594555</v>
       </c>
       <c r="C2" t="n">
-        <v>4.000621894805752</v>
+        <v>3.066979828067036</v>
       </c>
       <c r="D2" t="n">
-        <v>28.61598208338603</v>
+        <v>22.32297929916397</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="C3" t="n">
-        <v>32.57438882690916</v>
+        <v>24.38170423496954</v>
       </c>
       <c r="D3" t="n">
-        <v>57.70222131710628</v>
+        <v>49.98077562320512</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.3767954964483</v>
+        <v>30.87302005544944</v>
       </c>
       <c r="C4" t="n">
-        <v>68.45923091253859</v>
+        <v>53.27159392784043</v>
       </c>
       <c r="D4" t="n">
-        <v>44.13348629671111</v>
+        <v>52.26333903557895</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.59907138823559</v>
+        <v>32.7658296292373</v>
       </c>
       <c r="C5" t="n">
-        <v>77.3371754020425</v>
+        <v>46.4612101034803</v>
       </c>
       <c r="D5" t="n">
-        <v>34.72932503773092</v>
+        <v>41.11068511533519</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.09186767803848</v>
+        <v>24.43275511559037</v>
       </c>
       <c r="C6" t="n">
-        <v>75.35109979635121</v>
+        <v>36.66925850132262</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>42.75903951076558</v>
+        <v>24.97271635292611</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>22.94835258676919</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289648166866534</v>
+        <v>7.300695983251529</v>
       </c>
       <c r="C21" t="n">
-        <v>75.63009973124029</v>
+        <v>77.5698948220475</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378442146008217</v>
+        <v>6.388108985345088</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.18911745402114</v>
+        <v>5.027529993447916</v>
       </c>
       <c r="C2" t="n">
-        <v>9.106691704593414</v>
+        <v>4.890085314853362</v>
       </c>
       <c r="D2" t="n">
-        <v>32.00988389696725</v>
+        <v>17.55364895193297</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.94634803363169</v>
+        <v>19.82639488726434</v>
       </c>
       <c r="C3" t="n">
-        <v>22.26112919379642</v>
+        <v>16.61117115585603</v>
       </c>
       <c r="D3" t="n">
-        <v>67.20553909421541</v>
+        <v>56.65666001208342</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.8092064546734</v>
+        <v>37.85422798034851</v>
       </c>
       <c r="C4" t="n">
-        <v>76.21896476690537</v>
+        <v>58.08313942635404</v>
       </c>
       <c r="D4" t="n">
-        <v>63.11165116750621</v>
+        <v>66.32785664661876</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.93134408062751</v>
+        <v>40.5216364927871</v>
       </c>
       <c r="C5" t="n">
-        <v>104.7033926579224</v>
+        <v>76.74812677949441</v>
       </c>
       <c r="D5" t="n">
-        <v>42.48513190128072</v>
+        <v>51.24723016168351</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.53842401475054</v>
+        <v>35.98498035146259</v>
       </c>
       <c r="C6" t="n">
-        <v>102.1184509526405</v>
+        <v>58.20389439397641</v>
       </c>
       <c r="D6" t="n">
-        <v>36.91076843656734</v>
+        <v>40.69442408873454</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>79.4096448057075</v>
+        <v>41.14210104187108</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>41.55738032076748</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.62499773917349</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500983895300917</v>
+        <v>7.519908320762364</v>
       </c>
       <c r="C21" t="n">
-        <v>85.32369180904793</v>
+        <v>87.41893422886248</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500983895300917</v>
+        <v>7.519908320762364</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_32_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628608014</v>
+        <v>10.84497619967914</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907178115342</v>
+        <v>37.78907148009112</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.476188694288708</v>
+        <v>4.684900044665779</v>
       </c>
       <c r="C2" t="n">
-        <v>4.661338099763856</v>
+        <v>9.92939628075224</v>
       </c>
       <c r="D2" t="n">
-        <v>17.27090561310989</v>
+        <v>31.33444147644544</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.43231314723387</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C3" t="n">
-        <v>18.0052528958865</v>
+        <v>19.76749002500953</v>
       </c>
       <c r="D3" t="n">
-        <v>57.39297079026854</v>
+        <v>79.90935438716913</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.49236398810894</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="C4" t="n">
-        <v>48.71530283243098</v>
+        <v>73.33459001182824</v>
       </c>
       <c r="D4" t="n">
-        <v>78.43967807391167</v>
+        <v>103.6971012610693</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.1119289049467</v>
+        <v>39.09810232162923</v>
       </c>
       <c r="C5" t="n">
-        <v>92.84878912914211</v>
+        <v>121.4421910153305</v>
       </c>
       <c r="D5" t="n">
-        <v>63.59270754258716</v>
+        <v>79.10432126968676</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>37.27303333943441</v>
       </c>
       <c r="C6" t="n">
-        <v>92.61906016634835</v>
+        <v>126.1889411653638</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21519234034186</v>
+        <v>51.44161620712438</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.63820242768521</v>
+        <v>25.99078872223005</v>
       </c>
       <c r="C7" t="n">
-        <v>64.25833248606648</v>
+        <v>117.0783224699534</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.85660808191773</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C8" t="n">
-        <v>42.05807164993335</v>
+        <v>81.44578954431539</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.727180127212415</v>
+        <v>7.665678989535146</v>
       </c>
       <c r="C21" t="n">
-        <v>96.58975159015519</v>
+        <v>93.90456762180554</v>
       </c>
       <c r="D21" t="n">
-        <v>8.693077643113966</v>
+        <v>7.665678989535146</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.353691215436109</v>
+        <v>4.920519493685013</v>
       </c>
       <c r="C2" t="n">
-        <v>10.34958429816987</v>
+        <v>10.10218387669968</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67636741496382</v>
+        <v>34.15696612615503</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.43231314723387</v>
+        <v>15.9435827169682</v>
       </c>
       <c r="C3" t="n">
-        <v>18.0052528958865</v>
+        <v>29.13827186204533</v>
       </c>
       <c r="D3" t="n">
-        <v>57.61386402372407</v>
+        <v>84.97517254108267</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.65453228575891</v>
+        <v>31.61325782445154</v>
       </c>
       <c r="C4" t="n">
-        <v>46.26486056263094</v>
+        <v>61.47802298763951</v>
       </c>
       <c r="D4" t="n">
-        <v>88.27973531357743</v>
+        <v>117.5191271891602</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.87340527054373</v>
+        <v>42.90237467558562</v>
       </c>
       <c r="C5" t="n">
-        <v>91.32708018755955</v>
+        <v>126.57182277002</v>
       </c>
       <c r="D5" t="n">
-        <v>75.2755052231242</v>
+        <v>94.419585455937</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.31206656789281</v>
+        <v>44.19631814978292</v>
       </c>
       <c r="C6" t="n">
-        <v>120.2719477518683</v>
+        <v>157.1827161884356</v>
       </c>
       <c r="D6" t="n">
-        <v>55.8692983532775</v>
+        <v>62.75233150775189</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.95677170994669</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="C7" t="n">
-        <v>98.15415372289186</v>
+        <v>146.3029881299724</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.11939767148639</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>63.83814446864884</v>
+        <v>115.8265941470387</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.31406145436774</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>70.55624400880974</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.921563528361353</v>
+        <v>7.84076957803617</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9509121918331</v>
+        <v>101.9300045144702</v>
       </c>
       <c r="D21" t="n">
-        <v>9.90195441045169</v>
+        <v>8.82086577529069</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.00008211545801</v>
+        <v>7.292421947145307</v>
       </c>
       <c r="C2" t="n">
-        <v>7.845145904636262</v>
+        <v>11.86540275352695</v>
       </c>
       <c r="D2" t="n">
-        <v>15.88860484553038</v>
+        <v>29.62030998483052</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.96307880233289</v>
+        <v>15.83559046950105</v>
       </c>
       <c r="C3" t="n">
-        <v>29.09900195387546</v>
+        <v>33.4432355451676</v>
       </c>
       <c r="D3" t="n">
-        <v>57.92311455056181</v>
+        <v>89.82991493858316</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>30.29869764846506</v>
       </c>
       <c r="C4" t="n">
-        <v>45.11621574866217</v>
+        <v>65.6386697582375</v>
       </c>
       <c r="D4" t="n">
-        <v>95.63106212297755</v>
+        <v>127.7037778730166</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.87969666739671</v>
+        <v>44.39953992456201</v>
       </c>
       <c r="C5" t="n">
-        <v>88.33274968960677</v>
+        <v>119.2578023733813</v>
       </c>
       <c r="D5" t="n">
-        <v>86.76195336281188</v>
+        <v>110.4957041129785</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.79887456047898</v>
+        <v>50.11331156327844</v>
       </c>
       <c r="C6" t="n">
-        <v>130.9386365585099</v>
+        <v>176.1009944492716</v>
       </c>
       <c r="D6" t="n">
-        <v>65.48944410719199</v>
+        <v>73.6605302496382</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.61658828265855</v>
+        <v>41.74096714146164</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7268000385708</v>
+        <v>179.1208503875348</v>
       </c>
       <c r="D7" t="n">
-        <v>49.46633982617978</v>
+        <v>50.66407202536089</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.30012136452581</v>
+        <v>27.03733177495716</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>148.2880819879595</v>
       </c>
       <c r="D8" t="n">
-        <v>42.39186586937727</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.52656092684155</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>59.24061996966101</v>
+        <v>101.5078038805989</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>58.64960785170445</v>
       </c>
       <c r="D10" t="n">
-        <v>37.29659528433633</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>39.09319358310798</v>
       </c>
       <c r="D11" t="n">
         <v>36.42774856607789</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>36.66729500591412</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>32.00006641992479</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.102028302240784</v>
+        <v>7.999994721840025</v>
       </c>
       <c r="C21" t="n">
-        <v>114.4411497691511</v>
+        <v>109.9999274253004</v>
       </c>
       <c r="D21" t="n">
-        <v>11.14028891558108</v>
+        <v>9.999993402300031</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.873035750982671</v>
+        <v>6.542366701100745</v>
       </c>
       <c r="C2" t="n">
-        <v>5.083489612589984</v>
+        <v>8.163232160812228</v>
       </c>
       <c r="D2" t="n">
-        <v>12.91685454477528</v>
+        <v>24.55841882173396</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.88025214227767</v>
+        <v>19.90984344212531</v>
       </c>
       <c r="C3" t="n">
-        <v>40.39400929123502</v>
+        <v>49.41136195474197</v>
       </c>
       <c r="D3" t="n">
-        <v>65.16350386938204</v>
+        <v>97.01139939514857</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.36777984066083</v>
+        <v>21.32650537935346</v>
       </c>
       <c r="C4" t="n">
-        <v>70.51402885752717</v>
+        <v>94.81424803304421</v>
       </c>
       <c r="D4" t="n">
-        <v>94.57175635009524</v>
+        <v>123.0709104566759</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.93196597543326</v>
+        <v>28.2252464970958</v>
       </c>
       <c r="C5" t="n">
-        <v>78.22074833586463</v>
+        <v>105.2188102026519</v>
       </c>
       <c r="D5" t="n">
-        <v>64.10812508731674</v>
+        <v>73.70470889632931</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.89189424600839</v>
+        <v>25.92206638293279</v>
       </c>
       <c r="C6" t="n">
-        <v>88.07062305257288</v>
+        <v>117.9776033670435</v>
       </c>
       <c r="D6" t="n">
-        <v>32.56358960216246</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>65.99504417487908</v>
+        <v>104.2625879387155</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>43.64359419229195</v>
+        <v>74.76990515543707</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>44.70780870369548</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>28.47068342315751</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>24.89024954576939</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.17086515826795</v>
+        <v>3.964297229748621</v>
       </c>
       <c r="C2" t="n">
-        <v>2.125483779694344</v>
+        <v>3.73064127613788</v>
       </c>
       <c r="D2" t="n">
-        <v>10.03247978969815</v>
+        <v>17.02645043475243</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.68805057642355</v>
+        <v>21.82916020392783</v>
       </c>
       <c r="C3" t="n">
-        <v>29.7960428238907</v>
+        <v>41.79299976978672</v>
       </c>
       <c r="D3" t="n">
-        <v>61.2217868368311</v>
+        <v>95.85784584265856</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.19882142453914</v>
+        <v>28.35876418487337</v>
       </c>
       <c r="C4" t="n">
-        <v>88.98168492211391</v>
+        <v>110.7548855068997</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7263737657475</v>
+        <v>139.1008869716178</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.98167525545136</v>
+        <v>31.07231483941155</v>
       </c>
       <c r="C5" t="n">
-        <v>105.6851403621692</v>
+        <v>139.1627370769854</v>
       </c>
       <c r="D5" t="n">
-        <v>79.20249604011144</v>
+        <v>93.21694451823465</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.05668899160162</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>108.4379609248772</v>
+        <v>142.3701068267597</v>
       </c>
       <c r="D6" t="n">
-        <v>40.77492740048278</v>
+        <v>42.66675522656639</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>90.24912120829654</v>
+        <v>132.2296347895944</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>59.33192250615598</v>
+        <v>96.46652941929158</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>49.92187076095029</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.717698629533423</v>
+        <v>3.697261854193488</v>
       </c>
       <c r="C2" t="n">
-        <v>4.934263961544469</v>
+        <v>10.18759592696915</v>
       </c>
       <c r="D2" t="n">
-        <v>9.799805583791661</v>
+        <v>24.31690888648924</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.67484588791183</v>
+        <v>17.63218876827272</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5438314748905</v>
+        <v>27.67055904419635</v>
       </c>
       <c r="D3" t="n">
-        <v>55.81726572495241</v>
+        <v>87.95477682347175</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.80914970141117</v>
+        <v>34.80393786325368</v>
       </c>
       <c r="C4" t="n">
-        <v>81.89837523597318</v>
+        <v>107.4365782665454</v>
       </c>
       <c r="D4" t="n">
-        <v>111.7376149588507</v>
+        <v>152.8335738586222</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.81740459367266</v>
+        <v>36.30012136452582</v>
       </c>
       <c r="C5" t="n">
-        <v>136.1438628864265</v>
+        <v>170.2841393016093</v>
       </c>
       <c r="D5" t="n">
-        <v>97.04576056479723</v>
+        <v>117.1470448092507</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.26173539306896</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="C6" t="n">
-        <v>139.5122392596973</v>
+        <v>180.28716666018</v>
       </c>
       <c r="D6" t="n">
-        <v>53.89696721544566</v>
+        <v>57.9623844587317</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>123.7856227853676</v>
+        <v>165.7062497567064</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.6062624173348</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>88.45546815263761</v>
+        <v>132.5997536740954</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>54.80312034646543</v>
+        <v>79.98593070810035</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57777603837842</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.91916219754903</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.79680358741669</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.293763547748049</v>
+        <v>2.214822820780804</v>
       </c>
       <c r="C2" t="n">
-        <v>2.158863201638736</v>
+        <v>4.854742397500478</v>
       </c>
       <c r="D2" t="n">
-        <v>6.728898764907639</v>
+        <v>16.9459471230042</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.05772749256809</v>
+        <v>17.21003725544659</v>
       </c>
       <c r="C3" t="n">
-        <v>19.51714436042659</v>
+        <v>34.50352306575415</v>
       </c>
       <c r="D3" t="n">
-        <v>53.56906348222721</v>
+        <v>89.48139450357553</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.62895009218627</v>
+        <v>38.39026222686728</v>
       </c>
       <c r="C4" t="n">
-        <v>74.81506554983244</v>
+        <v>104.2714236680537</v>
       </c>
       <c r="D4" t="n">
-        <v>117.2255846255904</v>
+        <v>162.6608683781328</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.8362787842316</v>
+        <v>37.99363615435157</v>
       </c>
       <c r="C5" t="n">
-        <v>159.9021573291993</v>
+        <v>205.0380080319464</v>
       </c>
       <c r="D5" t="n">
-        <v>106.6914317590221</v>
+        <v>123.6020359646734</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.38499363544755</v>
+        <v>29.54471541160352</v>
       </c>
       <c r="C6" t="n">
-        <v>176.906027566754</v>
+        <v>212.8105046064684</v>
       </c>
       <c r="D6" t="n">
-        <v>53.25294072145974</v>
+        <v>56.35231822376692</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.95924962250714</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>127.1392729430747</v>
+        <v>174.0304885410151</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>69.84644041863932</v>
+        <v>97.88515485192822</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.69662426385451</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.052654523130833</v>
+        <v>2.791108723173682</v>
       </c>
       <c r="C2" t="n">
-        <v>4.315762907868979</v>
+        <v>6.089781009442965</v>
       </c>
       <c r="D2" t="n">
-        <v>10.66668880664159</v>
+        <v>13.84755136840126</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>12.63018421513522</v>
       </c>
       <c r="C3" t="n">
-        <v>13.46466976374501</v>
+        <v>26.73789872516188</v>
       </c>
       <c r="D3" t="n">
-        <v>47.01098881785852</v>
+        <v>83.67926557147689</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.24682925105601</v>
+        <v>35.7356164345839</v>
       </c>
       <c r="C4" t="n">
-        <v>61.72051467058848</v>
+        <v>95.38857044002859</v>
       </c>
       <c r="D4" t="n">
-        <v>117.4680763085394</v>
+        <v>168.4551433285974</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.38439710283758</v>
+        <v>46.2157731774186</v>
       </c>
       <c r="C5" t="n">
-        <v>150.4037482906114</v>
+        <v>200.7428618258666</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8474728907351</v>
+        <v>147.0903497887784</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.90325861229863</v>
+        <v>38.03781480104267</v>
       </c>
       <c r="C6" t="n">
-        <v>215.386610582412</v>
+        <v>266.023193672054</v>
       </c>
       <c r="D6" t="n">
-        <v>70.03788122096746</v>
+        <v>75.83411966684064</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>16.22927129890402</v>
       </c>
       <c r="C7" t="n">
-        <v>188.2236151013112</v>
+        <v>230.14424207265</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>113.2396889463483</v>
+        <v>150.7080900789279</v>
       </c>
       <c r="D8" t="n">
-        <v>34.88149593188918</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>64.45468202691582</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.44249047717483</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.96095107600838</v>
+        <v>1.892809573787851</v>
       </c>
       <c r="C2" t="n">
-        <v>2.758711048933538</v>
+        <v>3.62264902867073</v>
       </c>
       <c r="D2" t="n">
-        <v>8.071929624317274</v>
+        <v>10.78253503574272</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25283324380595</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C3" t="n">
-        <v>15.2661768010379</v>
+        <v>25.61870634232052</v>
       </c>
       <c r="D3" t="n">
-        <v>45.18493808795944</v>
+        <v>78.19620464325845</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.59294422229862</v>
+        <v>32.16205479112551</v>
       </c>
       <c r="C4" t="n">
-        <v>50.41274461307372</v>
+        <v>85.95692024532948</v>
       </c>
       <c r="D4" t="n">
-        <v>115.7068209271206</v>
+        <v>171.0715009604152</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.1339125695344</v>
+        <v>49.87278337573798</v>
       </c>
       <c r="C5" t="n">
-        <v>140.5617275555371</v>
+        <v>196.3495408493621</v>
       </c>
       <c r="D5" t="n">
-        <v>135.1866588747858</v>
+        <v>164.0991287648544</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.81145735418494</v>
+        <v>44.43782808502763</v>
       </c>
       <c r="C6" t="n">
-        <v>234.8281603696116</v>
+        <v>296.0911806100211</v>
       </c>
       <c r="D6" t="n">
-        <v>83.32092765942681</v>
+        <v>89.11716610529999</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>237.3306352677367</v>
+        <v>284.7608303553085</v>
       </c>
       <c r="D7" t="n">
-        <v>48.08894779712151</v>
+        <v>45.33416373900496</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>151.2922299629547</v>
+        <v>191.7647790705294</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>72.77499382040753</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.307328089158257</v>
+        <v>2.953097094374406</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75853112248429</v>
+        <v>12.05978879896782</v>
       </c>
       <c r="D2" t="n">
-        <v>17.41325903022567</v>
+        <v>12.19919697297087</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.17996292951343</v>
+        <v>9.056622571676826</v>
       </c>
       <c r="C3" t="n">
-        <v>12.91489104936679</v>
+        <v>20.24854640009046</v>
       </c>
       <c r="D3" t="n">
-        <v>41.60155896745859</v>
+        <v>71.0245376637355</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.9690924617454</v>
+        <v>27.49089921431918</v>
       </c>
       <c r="C4" t="n">
-        <v>44.4142661401257</v>
+        <v>76.18067660643975</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4523272875424</v>
+        <v>168.5572450898391</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.00490270965058</v>
+        <v>49.1119289049467</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3742294395592</v>
+        <v>180.0279852662589</v>
       </c>
       <c r="D5" t="n">
-        <v>142.3534171157875</v>
+        <v>181.2551698965674</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79.09450379264429</v>
+        <v>52.60891422747383</v>
       </c>
       <c r="C6" t="n">
-        <v>230.8432464380738</v>
+        <v>303.3364786673625</v>
       </c>
       <c r="D6" t="n">
-        <v>102.1184509526405</v>
+        <v>110.4102920627091</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.97484407925062</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="C7" t="n">
-        <v>285.6591295046944</v>
+        <v>341.1141303267797</v>
       </c>
       <c r="D7" t="n">
-        <v>57.97023844036566</v>
+        <v>55.095681162331</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>221.222118936455</v>
+        <v>263.8643304704152</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>114.3765527878661</v>
+        <v>130.57342641253</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>25.23287949455151</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.292601873594555</v>
+        <v>5.005931543954486</v>
       </c>
       <c r="C2" t="n">
-        <v>2.928553401768235</v>
+        <v>9.97848366596458</v>
       </c>
       <c r="D2" t="n">
-        <v>15.4821612959722</v>
+        <v>13.75134009338507</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.674681656995811</v>
+        <v>2.133337761328319</v>
       </c>
       <c r="C2" t="n">
-        <v>2.587886948394592</v>
+        <v>7.043058030266617</v>
       </c>
       <c r="D2" t="n">
-        <v>12.67632635723482</v>
+        <v>9.076257525761761</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55503161026472</v>
+        <v>12.40929098167968</v>
       </c>
       <c r="C3" t="n">
-        <v>16.74861583445059</v>
+        <v>30.70906818884023</v>
       </c>
       <c r="D3" t="n">
-        <v>48.6946861306418</v>
+        <v>75.95291113905448</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.09291584566751</v>
+        <v>37.40753277491622</v>
       </c>
       <c r="C4" t="n">
-        <v>64.28582142178539</v>
+        <v>108.2278669161684</v>
       </c>
       <c r="D4" t="n">
-        <v>117.81266975273</v>
+        <v>173.1007734650933</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.49833658979244</v>
+        <v>30.53235360207581</v>
       </c>
       <c r="C5" t="n">
-        <v>186.8756755033804</v>
+        <v>260.8749087109837</v>
       </c>
       <c r="D5" t="n">
-        <v>135.1130277969673</v>
+        <v>164.1482161500667</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="C6" t="n">
-        <v>240.1816306008695</v>
+        <v>281.1578162807228</v>
       </c>
       <c r="D6" t="n">
-        <v>83.84419918579036</v>
+        <v>84.56872899152451</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>155.525526063667</v>
+        <v>185.5287176531537</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.253110981246429</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>84.28304040958866</v>
+        <v>96.21618375470864</v>
       </c>
       <c r="D8" t="n">
-        <v>25.78560345204247</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>20.96718571959912</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.77302065833652</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>19.78712497909446</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.94732978133594</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.71617710248143</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.539822368615503</v>
+        <v>6.480516595733195</v>
       </c>
       <c r="C2" t="n">
-        <v>3.11508546557513</v>
+        <v>4.78012957197772</v>
       </c>
       <c r="D2" t="n">
-        <v>15.81791901082461</v>
+        <v>21.93911594680347</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.24591995214721</v>
+        <v>10.63723637551419</v>
       </c>
       <c r="C3" t="n">
-        <v>7.37783399741478</v>
+        <v>25.14255870576082</v>
       </c>
       <c r="D3" t="n">
-        <v>16.13993225781756</v>
+        <v>14.68694565553228</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39793269759716</v>
+        <v>13.39706991686143</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14211824036163</v>
+        <v>70.13760132945103</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576227376187902</v>
+        <v>1.576125872571933</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.084471360294231</v>
+        <v>4.247040568571702</v>
       </c>
       <c r="C2" t="n">
-        <v>3.567671157232909</v>
+        <v>5.187554869240146</v>
       </c>
       <c r="D2" t="n">
-        <v>14.05371838629309</v>
+        <v>27.09329139409923</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.07183181332604</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="C3" t="n">
-        <v>10.41634314205866</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D3" t="n">
-        <v>25.52544031041707</v>
+        <v>29.56533211339269</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.13283903970958</v>
+        <v>12.44365215132832</v>
       </c>
       <c r="C4" t="n">
-        <v>11.98419422574081</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D4" t="n">
-        <v>23.53445596620454</v>
+        <v>22.76869275689203</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44251875943188</v>
+        <v>15.43728620302194</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15299939472523</v>
+        <v>86.1238072379119</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251056580933028</v>
+        <v>3.249954990109883</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.480115685105695</v>
+        <v>4.414919425997907</v>
       </c>
       <c r="C2" t="n">
-        <v>5.509568116233099</v>
+        <v>8.052294670232339</v>
       </c>
       <c r="D2" t="n">
-        <v>13.67967251097506</v>
+        <v>19.76847177271377</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.88882582970863</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="C3" t="n">
-        <v>12.51728322914683</v>
+        <v>20.52834449580081</v>
       </c>
       <c r="D3" t="n">
-        <v>30.84651286743478</v>
+        <v>44.37990497047706</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.59300097556086</v>
+        <v>24.77243982125977</v>
       </c>
       <c r="C4" t="n">
-        <v>20.16509784522949</v>
+        <v>46.54564040604553</v>
       </c>
       <c r="D4" t="n">
-        <v>30.8092064546734</v>
+        <v>32.45559735469531</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.85460352878024</v>
+        <v>11.09374905798896</v>
       </c>
       <c r="C5" t="n">
-        <v>15.11891464540088</v>
+        <v>43.27053006467818</v>
       </c>
       <c r="D5" t="n">
-        <v>31.31775176547326</v>
+        <v>30.82687791334985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74158726413862</v>
+        <v>16.72608326584129</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1236823112456</v>
+        <v>102.0291079216318</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022476179241587</v>
+        <v>4.181520816460321</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.752059799182062</v>
+        <v>4.926409979910495</v>
       </c>
       <c r="C2" t="n">
-        <v>9.006553438760239</v>
+        <v>7.58694625841935</v>
       </c>
       <c r="D2" t="n">
-        <v>19.99034675387355</v>
+        <v>31.49937509075891</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.88882582970863</v>
+        <v>15.47725255745097</v>
       </c>
       <c r="C3" t="n">
-        <v>17.72545480017616</v>
+        <v>26.70353755551324</v>
       </c>
       <c r="D3" t="n">
-        <v>34.3808046027233</v>
+        <v>49.52917167925159</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.77466535857552</v>
+        <v>27.89930625928586</v>
       </c>
       <c r="C4" t="n">
-        <v>26.50816976236813</v>
+        <v>49.23857435879452</v>
       </c>
       <c r="D4" t="n">
-        <v>38.5817030291954</v>
+        <v>46.58392856651115</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.80171232593793</v>
+        <v>24.1019061392592</v>
       </c>
       <c r="C5" t="n">
-        <v>27.14532402242431</v>
+        <v>66.31705742187205</v>
       </c>
       <c r="D5" t="n">
-        <v>35.44109212330986</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.18996033300515</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>18.55601335796896</v>
+        <v>41.29819892684633</v>
       </c>
       <c r="D6" t="n">
         <v>38.44033135978387</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07829052543728</v>
+        <v>18.04655423540482</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9393239040432</v>
+        <v>117.7322823928791</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886967819214202</v>
+        <v>6.015518078468275</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.878124415953153</v>
+        <v>5.53411180883927</v>
       </c>
       <c r="C2" t="n">
-        <v>5.998478472948011</v>
+        <v>10.9415781638307</v>
       </c>
       <c r="D2" t="n">
-        <v>23.23894990722625</v>
+        <v>30.22015783212532</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3131207643925</v>
+        <v>14.47586989911922</v>
       </c>
       <c r="C3" t="n">
-        <v>26.15375884113503</v>
+        <v>26.50227927614264</v>
       </c>
       <c r="D3" t="n">
-        <v>39.44171401811561</v>
+        <v>58.75269136065037</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.39781310886498</v>
+        <v>21.16059001733575</v>
       </c>
       <c r="C4" t="n">
-        <v>30.54118933141402</v>
+        <v>48.85569275413827</v>
       </c>
       <c r="D4" t="n">
-        <v>40.36848385092459</v>
+        <v>52.46754255806228</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.6846633649543</v>
+        <v>20.10128424445345</v>
       </c>
       <c r="C5" t="n">
-        <v>29.25608158655496</v>
+        <v>59.101211795658</v>
       </c>
       <c r="D5" t="n">
-        <v>33.57577148524092</v>
+        <v>34.87658719336795</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.08178815908875</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>21.37362926915731</v>
+        <v>49.99255659565609</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>31.71830482880595</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>15.69029180927252</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5983,10 +5983,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.070967657508074</v>
+        <v>7.050473106191875</v>
       </c>
       <c r="C21" t="n">
-        <v>67.1741927463267</v>
+        <v>66.97949450882281</v>
       </c>
       <c r="D21" t="n">
-        <v>5.303225743131056</v>
+        <v>4.406545691369922</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.292601873594555</v>
+        <v>5.324017800130453</v>
       </c>
       <c r="C2" t="n">
-        <v>3.066979828067036</v>
+        <v>5.572399969304896</v>
       </c>
       <c r="D2" t="n">
-        <v>22.32297929916397</v>
+        <v>24.75967710110456</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.6377194015997</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="C3" t="n">
-        <v>24.38170423496954</v>
+        <v>37.23769042208152</v>
       </c>
       <c r="D3" t="n">
-        <v>49.98077562320512</v>
+        <v>69.93970645054277</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.87302005544944</v>
+        <v>25.67859295227957</v>
       </c>
       <c r="C4" t="n">
-        <v>53.27159392784043</v>
+        <v>59.29559784109885</v>
       </c>
       <c r="D4" t="n">
-        <v>52.26333903557895</v>
+        <v>70.57784245830319</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.7658296292373</v>
+        <v>26.80171232593793</v>
       </c>
       <c r="C5" t="n">
-        <v>46.4612101034803</v>
+        <v>78.26983572107697</v>
       </c>
       <c r="D5" t="n">
-        <v>41.11068511533519</v>
+        <v>47.1238898038469</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.43275511559037</v>
+        <v>20.64909946342317</v>
       </c>
       <c r="C6" t="n">
-        <v>36.66925850132262</v>
+        <v>75.95487463446298</v>
       </c>
       <c r="D6" t="n">
-        <v>35.783722072092</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.43834250217959</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>24.97271635292611</v>
+        <v>53.05953642372311</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>20.36144738607885</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.300695983251529</v>
+        <v>7.26931907438225</v>
       </c>
       <c r="C21" t="n">
-        <v>77.5698948220475</v>
+        <v>76.32785028101362</v>
       </c>
       <c r="D21" t="n">
-        <v>6.388108985345088</v>
+        <v>5.451989305786688</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.027529993447916</v>
+        <v>4.478733026773948</v>
       </c>
       <c r="C2" t="n">
-        <v>4.890085314853362</v>
+        <v>3.379175598017521</v>
       </c>
       <c r="D2" t="n">
-        <v>17.55364895193297</v>
+        <v>30.6099116707113</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.82639488726434</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C3" t="n">
-        <v>16.61117115585603</v>
+        <v>27.94053966286423</v>
       </c>
       <c r="D3" t="n">
-        <v>56.65666001208342</v>
+        <v>73.5181768325224</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.85422798034851</v>
+        <v>30.12001956629214</v>
       </c>
       <c r="C4" t="n">
-        <v>58.08313942635404</v>
+        <v>78.95018688012</v>
       </c>
       <c r="D4" t="n">
-        <v>66.32785664661876</v>
+        <v>89.78573629189205</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.5216364927871</v>
+        <v>33.37942194439156</v>
       </c>
       <c r="C5" t="n">
-        <v>76.74812677949441</v>
+        <v>95.10680884890976</v>
       </c>
       <c r="D5" t="n">
-        <v>51.24723016168351</v>
+        <v>61.85010536754907</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.98498035146259</v>
+        <v>28.94094057349173</v>
       </c>
       <c r="C6" t="n">
-        <v>58.20389439397641</v>
+        <v>102.7222257907523</v>
       </c>
       <c r="D6" t="n">
-        <v>40.69442408873454</v>
+        <v>42.38499363544755</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>41.14210104187108</v>
+        <v>84.14068699247288</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>27.95526587842792</v>
+        <v>50.98706702005809</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.519908320762364</v>
+        <v>7.475017641109688</v>
       </c>
       <c r="C21" t="n">
-        <v>87.41893422886248</v>
+        <v>85.0283256676227</v>
       </c>
       <c r="D21" t="n">
-        <v>7.519908320762364</v>
+        <v>6.540640435970977</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_32_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619967914</v>
+        <v>10.84497634680921</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907148009112</v>
+        <v>37.78907199276249</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.684900044665779</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="C2" t="n">
-        <v>9.92939628075224</v>
+        <v>2.343431770037137</v>
       </c>
       <c r="D2" t="n">
-        <v>31.33444147644544</v>
+        <v>15.91020329502381</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>6.081927027808991</v>
       </c>
       <c r="C3" t="n">
-        <v>19.76749002500953</v>
+        <v>31.08213231645402</v>
       </c>
       <c r="D3" t="n">
-        <v>79.90935438716913</v>
+        <v>84.80827543136071</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.11100391050467</v>
+        <v>10.29951516525329</v>
       </c>
       <c r="C4" t="n">
-        <v>73.33459001182824</v>
+        <v>101.9486085998058</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6971012610693</v>
+        <v>96.65207973539424</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.09810232162923</v>
+        <v>10.16108873895449</v>
       </c>
       <c r="C5" t="n">
-        <v>121.4421910153305</v>
+        <v>129.7625028088222</v>
       </c>
       <c r="D5" t="n">
-        <v>79.10432126968676</v>
+        <v>52.59713325502288</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>7.647814616082655</v>
       </c>
       <c r="C6" t="n">
-        <v>126.1889411653638</v>
+        <v>84.20646408865744</v>
       </c>
       <c r="D6" t="n">
-        <v>51.44161620712438</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>117.0783224699534</v>
+        <v>45.21439051908685</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>81.44578954431539</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.665678989535146</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.90456762180554</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.665678989535146</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.920519493685013</v>
+        <v>0.7618362184955249</v>
       </c>
       <c r="C2" t="n">
-        <v>10.10218387669968</v>
+        <v>6.162430339557228</v>
       </c>
       <c r="D2" t="n">
-        <v>34.15696612615503</v>
+        <v>15.32409991558846</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.9435827169682</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C3" t="n">
-        <v>29.13827186204533</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D3" t="n">
-        <v>84.97517254108267</v>
+        <v>78.03421627205773</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.61325782445154</v>
+        <v>11.19290557611789</v>
       </c>
       <c r="C4" t="n">
-        <v>61.47802298763951</v>
+        <v>88.45841339575036</v>
       </c>
       <c r="D4" t="n">
-        <v>117.5191271891602</v>
+        <v>116.2939060542602</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="C5" t="n">
-        <v>126.57182277002</v>
+        <v>162.6510509010903</v>
       </c>
       <c r="D5" t="n">
-        <v>94.419585455937</v>
+        <v>74.02377690020951</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.19631814978292</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>157.1827161884356</v>
+        <v>147.0795505640317</v>
       </c>
       <c r="D6" t="n">
-        <v>62.75233150775189</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>146.3029881299724</v>
+        <v>83.30227445304611</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>115.8265941470387</v>
+        <v>44.56152829576272</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>38.72012945549421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.84076957803617</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9300045144702</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.82086577529069</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.292421947145307</v>
+        <v>0.4015348110369454</v>
       </c>
       <c r="C2" t="n">
-        <v>11.86540275352695</v>
+        <v>2.628138604268711</v>
       </c>
       <c r="D2" t="n">
-        <v>29.62030998483052</v>
+        <v>10.45954004104552</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.83559046950105</v>
+        <v>4.015348110369454</v>
       </c>
       <c r="C3" t="n">
-        <v>33.4432355451676</v>
+        <v>22.46729621168826</v>
       </c>
       <c r="D3" t="n">
-        <v>89.82991493858316</v>
+        <v>75.86455384567226</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.29869764846506</v>
+        <v>12.22668590868978</v>
       </c>
       <c r="C4" t="n">
-        <v>65.6386697582375</v>
+        <v>80.43066241812419</v>
       </c>
       <c r="D4" t="n">
-        <v>127.7037778730166</v>
+        <v>127.4740489102228</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.39953992456201</v>
+        <v>13.10633185169492</v>
       </c>
       <c r="C5" t="n">
-        <v>119.2578023733813</v>
+        <v>183.9304323906399</v>
       </c>
       <c r="D5" t="n">
-        <v>110.4957041129785</v>
+        <v>83.89034132788996</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.11331156327844</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>176.1009944492716</v>
+        <v>186.2041600736756</v>
       </c>
       <c r="D6" t="n">
-        <v>73.6605302496382</v>
+        <v>39.60762938013333</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.74096714146164</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>179.1208503875348</v>
+        <v>78.81077870611695</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.03733177495716</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>148.2880819879595</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>101.5078038805989</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>58.64960785170445</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.999994721840025</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.9999274253004</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.999993402300031</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.542366701100745</v>
+        <v>0.300414797499524</v>
       </c>
       <c r="C2" t="n">
-        <v>8.163232160812228</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55841882173396</v>
+        <v>9.463066121235006</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.90984344212531</v>
+        <v>2.670353755551325</v>
       </c>
       <c r="C3" t="n">
-        <v>49.41136195474197</v>
+        <v>15.70305452942773</v>
       </c>
       <c r="D3" t="n">
-        <v>97.01139939514857</v>
+        <v>67.66696051521141</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.32650537935346</v>
+        <v>10.06978620245953</v>
       </c>
       <c r="C4" t="n">
-        <v>94.81424803304421</v>
+        <v>68.11463746834795</v>
       </c>
       <c r="D4" t="n">
-        <v>123.0709104566759</v>
+        <v>135.6549525297115</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.2252464970958</v>
+        <v>15.87976911619216</v>
       </c>
       <c r="C5" t="n">
-        <v>105.2188102026519</v>
+        <v>167.5352457297182</v>
       </c>
       <c r="D5" t="n">
-        <v>73.70470889632931</v>
+        <v>107.6486357706628</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.92206638293279</v>
+        <v>12.88052987971816</v>
       </c>
       <c r="C6" t="n">
-        <v>117.9776033670435</v>
+        <v>239.336345827513</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>54.50074205355744</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>104.2625879387155</v>
+        <v>167.6825078853552</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>74.76990515543707</v>
+        <v>70.18023463808323</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>44.70780870369548</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.964297229748621</v>
+        <v>0.2002765316663493</v>
       </c>
       <c r="C2" t="n">
         <v>3.73064127613788</v>
       </c>
       <c r="D2" t="n">
-        <v>17.02645043475243</v>
+        <v>8.411614329986671</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.82916020392783</v>
+        <v>1.958586669972387</v>
       </c>
       <c r="C3" t="n">
-        <v>41.79299976978672</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="D3" t="n">
-        <v>95.85784584265856</v>
+        <v>61.64884708817846</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.35876418487337</v>
+        <v>8.321293541195963</v>
       </c>
       <c r="C4" t="n">
-        <v>110.7548855068997</v>
+        <v>56.0793923619863</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1008869716178</v>
+        <v>138.6286663258751</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.07231483941155</v>
+        <v>16.61607989437727</v>
       </c>
       <c r="C5" t="n">
-        <v>139.1627370769854</v>
+        <v>155.386117889664</v>
       </c>
       <c r="D5" t="n">
-        <v>93.21694451823465</v>
+        <v>125.5655313731671</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>15.65789413503238</v>
       </c>
       <c r="C6" t="n">
-        <v>142.3701068267597</v>
+        <v>264.0911141900963</v>
       </c>
       <c r="D6" t="n">
-        <v>42.66675522656639</v>
+        <v>66.61649047166733</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>132.2296347895944</v>
+        <v>232.6594796909303</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>96.46652941929158</v>
+        <v>108.6500184289945</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>48.25780840225195</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.697261854193488</v>
+        <v>0.2689988709636261</v>
       </c>
       <c r="C2" t="n">
-        <v>10.18759592696915</v>
+        <v>16.17822041828319</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31690888648924</v>
+        <v>12.96986892080461</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63218876827272</v>
+        <v>1.325359400733194</v>
       </c>
       <c r="C3" t="n">
-        <v>27.67055904419635</v>
+        <v>16.6357148484622</v>
       </c>
       <c r="D3" t="n">
-        <v>87.95477682347175</v>
+        <v>54.84042675922683</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.80393786325368</v>
+        <v>6.126105674500097</v>
       </c>
       <c r="C4" t="n">
-        <v>107.4365782665454</v>
+        <v>52.39096623713103</v>
       </c>
       <c r="D4" t="n">
-        <v>152.8335738586222</v>
+        <v>137.9394794374938</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.30012136452582</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C5" t="n">
-        <v>170.2841393016093</v>
+        <v>130.6951631278567</v>
       </c>
       <c r="D5" t="n">
-        <v>117.1470448092507</v>
+        <v>143.4087958978529</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.82397372796611</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="C6" t="n">
-        <v>180.28716666018</v>
+        <v>257.570345938489</v>
       </c>
       <c r="D6" t="n">
-        <v>57.9623844587317</v>
+        <v>85.77627866774809</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>11.61800233205675</v>
       </c>
       <c r="C7" t="n">
-        <v>165.7062497567064</v>
+        <v>302.3674936832709</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>48.20872101703962</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>132.5997536740954</v>
+        <v>194.1013386066369</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>79.98593070810035</v>
+        <v>83.53593040665682</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.214822820780804</v>
+        <v>0.1826050729899067</v>
       </c>
       <c r="C2" t="n">
-        <v>4.854742397500478</v>
+        <v>8.542186774651496</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9459471230042</v>
+        <v>9.442449419445822</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.21003725544659</v>
+        <v>1.948769192929919</v>
       </c>
       <c r="C3" t="n">
-        <v>34.50352306575415</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="D3" t="n">
-        <v>89.48139450357553</v>
+        <v>59.86206626644926</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.39026222686728</v>
+        <v>10.26122700478766</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2714236680537</v>
+        <v>75.19794715448869</v>
       </c>
       <c r="D4" t="n">
-        <v>162.6608683781328</v>
+        <v>142.2660415701095</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.99363615435157</v>
+        <v>11.46190444708151</v>
       </c>
       <c r="C5" t="n">
-        <v>205.0380080319464</v>
+        <v>207.2960277517141</v>
       </c>
       <c r="D5" t="n">
-        <v>123.6020359646734</v>
+        <v>131.1124059021616</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.54471541160352</v>
+        <v>7.205046401467343</v>
       </c>
       <c r="C6" t="n">
-        <v>212.8105046064684</v>
+        <v>259.7439353556914</v>
       </c>
       <c r="D6" t="n">
-        <v>56.35231822376692</v>
+        <v>69.83662294159687</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.785259294677205</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>174.0304885410151</v>
+        <v>136.4815840966873</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>97.88515485192822</v>
+        <v>61.50158493254144</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.791108723173682</v>
+        <v>0.09326603190344698</v>
       </c>
       <c r="C2" t="n">
-        <v>6.089781009442965</v>
+        <v>4.794855787541421</v>
       </c>
       <c r="D2" t="n">
-        <v>13.84755136840126</v>
+        <v>6.591454086313084</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.63018421513522</v>
+        <v>1.286089492563322</v>
       </c>
       <c r="C3" t="n">
-        <v>26.73789872516188</v>
+        <v>34.32680847898973</v>
       </c>
       <c r="D3" t="n">
-        <v>83.67926557147689</v>
+        <v>53.74577806899164</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.7356164345839</v>
+        <v>6.662139921018855</v>
       </c>
       <c r="C4" t="n">
-        <v>95.38857044002859</v>
+        <v>79.37135664524189</v>
       </c>
       <c r="D4" t="n">
-        <v>168.4551433285974</v>
+        <v>134.5573585963636</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.2157731774186</v>
+        <v>10.62741889847172</v>
       </c>
       <c r="C5" t="n">
-        <v>200.7428618258666</v>
+        <v>156.6133025199724</v>
       </c>
       <c r="D5" t="n">
-        <v>147.0903497887784</v>
+        <v>136.5365619681252</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.03781480104267</v>
+        <v>6.84278149860027</v>
       </c>
       <c r="C6" t="n">
-        <v>266.023193672054</v>
+        <v>243.9250345971626</v>
       </c>
       <c r="D6" t="n">
-        <v>75.83411966684064</v>
+        <v>75.63286138747003</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>2.87455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>230.14424207265</v>
+        <v>173.7310554912198</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>150.7080900789279</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.892809573787851</v>
+        <v>0.170824100538945</v>
       </c>
       <c r="C2" t="n">
-        <v>3.62264902867073</v>
+        <v>4.151811041259761</v>
       </c>
       <c r="D2" t="n">
-        <v>10.78253503574272</v>
+        <v>12.93452600345173</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.43245201595411</v>
+        <v>0.755945732270044</v>
       </c>
       <c r="C3" t="n">
-        <v>25.61870634232052</v>
+        <v>25.09838005906971</v>
       </c>
       <c r="D3" t="n">
-        <v>78.19620464325845</v>
+        <v>46.79991306144545</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.16205479112551</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C4" t="n">
-        <v>85.95692024532948</v>
+        <v>83.12359637087319</v>
       </c>
       <c r="D4" t="n">
-        <v>171.0715009604152</v>
+        <v>131.4049667180271</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.87278337573798</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="C5" t="n">
-        <v>196.3495408493621</v>
+        <v>152.7353990881975</v>
       </c>
       <c r="D5" t="n">
-        <v>164.0991287648544</v>
+        <v>153.4962535589888</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.43782808502763</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="C6" t="n">
-        <v>296.0911806100211</v>
+        <v>247.7086902493297</v>
       </c>
       <c r="D6" t="n">
-        <v>89.11716610529999</v>
+        <v>98.7775635150886</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.55244622005047</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>284.7608303553085</v>
+        <v>268.0524661767321</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>47.25053525769474</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>191.7647790705294</v>
+        <v>150.4577444143449</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>58.242182554442</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.74218556887735</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.953097094374406</v>
+        <v>0.2758711048933537</v>
       </c>
       <c r="C2" t="n">
-        <v>12.05978879896782</v>
+        <v>16.69265621530852</v>
       </c>
       <c r="D2" t="n">
-        <v>12.19919697297087</v>
+        <v>24.04201952930014</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.056622571676826</v>
+        <v>0.657770961845363</v>
       </c>
       <c r="C3" t="n">
-        <v>20.24854640009046</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0245376637355</v>
+        <v>46.15195957664255</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.49089921431918</v>
+        <v>2.973713796163589</v>
       </c>
       <c r="C4" t="n">
-        <v>76.18067660643975</v>
+        <v>72.46672504127406</v>
       </c>
       <c r="D4" t="n">
-        <v>168.5572450898391</v>
+        <v>125.7255562489593</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.1119289049467</v>
+        <v>8.884816723433635</v>
       </c>
       <c r="C5" t="n">
-        <v>180.0279852662589</v>
+        <v>152.9562923216531</v>
       </c>
       <c r="D5" t="n">
-        <v>181.2551698965674</v>
+        <v>165.0072453912827</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.60891422747383</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="C6" t="n">
-        <v>303.3364786673625</v>
+        <v>244.0457895647849</v>
       </c>
       <c r="D6" t="n">
-        <v>110.4102920627091</v>
+        <v>119.9499345048753</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.70942804173872</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>341.1141303267797</v>
+        <v>314.2250424551638</v>
       </c>
       <c r="D7" t="n">
-        <v>55.095681162331</v>
+        <v>62.40184757733576</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>263.8643304704152</v>
+        <v>248.760142040578</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>34.88149593188918</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>130.57342641253</v>
+        <v>117.9265524864226</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.62812290873548</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.005931543954486</v>
+        <v>2.020436775339935</v>
       </c>
       <c r="C2" t="n">
-        <v>9.97848366596458</v>
+        <v>11.27242714016188</v>
       </c>
       <c r="D2" t="n">
-        <v>13.75134009338507</v>
+        <v>11.63960078155018</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.133337761328319</v>
+        <v>0.460439673291754</v>
       </c>
       <c r="C2" t="n">
-        <v>7.043058030266617</v>
+        <v>13.0808064113845</v>
       </c>
       <c r="D2" t="n">
-        <v>9.076257525761761</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40929098167968</v>
+        <v>0.7706719478337462</v>
       </c>
       <c r="C3" t="n">
-        <v>30.70906818884023</v>
+        <v>41.65555509119216</v>
       </c>
       <c r="D3" t="n">
-        <v>75.95291113905448</v>
+        <v>52.6020419935441</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.40753277491622</v>
+        <v>2.156899706230242</v>
       </c>
       <c r="C4" t="n">
-        <v>108.2278669161684</v>
+        <v>61.95024363338223</v>
       </c>
       <c r="D4" t="n">
-        <v>173.1007734650933</v>
+        <v>121.0161125116873</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.53235360207581</v>
+        <v>7.044039777970866</v>
       </c>
       <c r="C5" t="n">
-        <v>260.8749087109837</v>
+        <v>143.8996697499763</v>
       </c>
       <c r="D5" t="n">
-        <v>164.1482161500667</v>
+        <v>169.4496537529995</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.58368222013712</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="C6" t="n">
-        <v>281.1578162807228</v>
+        <v>242.2344650504495</v>
       </c>
       <c r="D6" t="n">
-        <v>84.56872899152451</v>
+        <v>140.0355107860608</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>11.07902284242525</v>
       </c>
       <c r="C7" t="n">
-        <v>185.5287176531537</v>
+        <v>334.1672835715293</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>77.07406701730434</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>96.21618375470864</v>
+        <v>320.2755535564369</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>199.1327955909017</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>83.56145584696728</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.480516595733195</v>
+        <v>3.200497515844602</v>
       </c>
       <c r="C2" t="n">
-        <v>4.78012957197772</v>
+        <v>8.945685081096936</v>
       </c>
       <c r="D2" t="n">
-        <v>21.93911594680347</v>
+        <v>26.22837166665779</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.63723637551419</v>
+        <v>3.352668410002858</v>
       </c>
       <c r="C3" t="n">
-        <v>25.14255870576082</v>
+        <v>22.25622045527519</v>
       </c>
       <c r="D3" t="n">
-        <v>14.68694565553228</v>
+        <v>10.96121311791564</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39706991686143</v>
+        <v>11.67787382783725</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13760132945103</v>
+        <v>59.94641898289787</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576125872571933</v>
+        <v>0.7785249218558166</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.247040568571702</v>
+        <v>1.771072858461246</v>
       </c>
       <c r="C2" t="n">
-        <v>5.187554869240146</v>
+        <v>6.757369448330795</v>
       </c>
       <c r="D2" t="n">
-        <v>27.09329139409923</v>
+        <v>25.39584961345649</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65673246087889</v>
+        <v>8.22704576158827</v>
       </c>
       <c r="C3" t="n">
-        <v>21.07321447165778</v>
+        <v>30.7336118814464</v>
       </c>
       <c r="D3" t="n">
-        <v>29.56533211339269</v>
+        <v>31.28829933434585</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.44365215132832</v>
+        <v>4.377613013236528</v>
       </c>
       <c r="C4" t="n">
-        <v>38.86248287260999</v>
+        <v>36.70558316637975</v>
       </c>
       <c r="D4" t="n">
-        <v>22.76869275689203</v>
+        <v>20.01194520336698</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43728620302194</v>
+        <v>13.62731917733694</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1238072379119</v>
+        <v>73.7478449597058</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249954990109883</v>
+        <v>1.60321402086317</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.414919425997907</v>
+        <v>1.34204911170539</v>
       </c>
       <c r="C2" t="n">
-        <v>8.052294670232339</v>
+        <v>8.332092765942679</v>
       </c>
       <c r="D2" t="n">
-        <v>19.76847177271377</v>
+        <v>24.86570585316321</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.99267010218054</v>
+        <v>7.044039777970865</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52834449580081</v>
+        <v>27.96508335547039</v>
       </c>
       <c r="D3" t="n">
-        <v>44.37990497047706</v>
+        <v>45.05731088640736</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.77243982125977</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="C4" t="n">
-        <v>46.54564040604553</v>
+        <v>61.64393834965723</v>
       </c>
       <c r="D4" t="n">
-        <v>32.45559735469531</v>
+        <v>31.76641046631405</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.09374905798896</v>
+        <v>4.761476365597031</v>
       </c>
       <c r="C5" t="n">
-        <v>43.27053006467818</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D5" t="n">
-        <v>30.82687791334985</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72608326584129</v>
+        <v>14.83509815327418</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0291079216318</v>
+        <v>87.36224468039242</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181520816460321</v>
+        <v>2.472516358879031</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.926409979910495</v>
+        <v>1.142754327743287</v>
       </c>
       <c r="C2" t="n">
-        <v>7.58694625841935</v>
+        <v>5.057964172279567</v>
       </c>
       <c r="D2" t="n">
-        <v>31.49937509075891</v>
+        <v>33.5944246916216</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.47725255745097</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C3" t="n">
-        <v>26.70353755551324</v>
+        <v>30.66979828067036</v>
       </c>
       <c r="D3" t="n">
-        <v>49.52917167925159</v>
+        <v>54.49190632421922</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.89930625928586</v>
+        <v>12.76272015520853</v>
       </c>
       <c r="C4" t="n">
-        <v>49.23857435879452</v>
+        <v>66.62139921018856</v>
       </c>
       <c r="D4" t="n">
-        <v>46.58392856651115</v>
+        <v>47.18377641380595</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.1019061392592</v>
+        <v>11.09374905798896</v>
       </c>
       <c r="C5" t="n">
-        <v>66.31705742187205</v>
+        <v>83.30129270534188</v>
       </c>
       <c r="D5" t="n">
-        <v>35.04839304161113</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>5.635231822376692</v>
       </c>
       <c r="C6" t="n">
-        <v>41.29819892684633</v>
+        <v>41.82147045320988</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04655423540482</v>
+        <v>16.07327765369442</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7322823928791</v>
+        <v>100.6694758310335</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015518078468275</v>
+        <v>3.383847927093563</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.53411180883927</v>
+        <v>1.297870465014283</v>
       </c>
       <c r="C2" t="n">
-        <v>10.9415781638307</v>
+        <v>5.362305960596078</v>
       </c>
       <c r="D2" t="n">
-        <v>30.22015783212532</v>
+        <v>34.99243342246906</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.47586989911922</v>
+        <v>4.717297718905924</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50227927614264</v>
+        <v>24.5780537758189</v>
       </c>
       <c r="D3" t="n">
-        <v>58.75269136065037</v>
+        <v>67.90257996423064</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.16059001733575</v>
+        <v>11.76722798310227</v>
       </c>
       <c r="C4" t="n">
-        <v>48.85569275413827</v>
+        <v>71.52228374978863</v>
       </c>
       <c r="D4" t="n">
-        <v>52.46754255806228</v>
+        <v>62.98402396595412</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.10128424445345</v>
+        <v>15.24163310843173</v>
       </c>
       <c r="C5" t="n">
-        <v>59.101211795658</v>
+        <v>104.801567428347</v>
       </c>
       <c r="D5" t="n">
-        <v>34.87658719336795</v>
+        <v>41.03705403751668</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.7132318593687</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>49.99255659565609</v>
+        <v>88.67439789068467</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>26.11056194214817</v>
+        <v>39.46527596301753</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050473106191875</v>
+        <v>17.3343592825225</v>
       </c>
       <c r="C21" t="n">
-        <v>66.97949450882281</v>
+        <v>114.4067712646485</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406545691369922</v>
+        <v>4.333589820630624</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.324017800130453</v>
+        <v>1.707259257685203</v>
       </c>
       <c r="C2" t="n">
-        <v>5.572399969304896</v>
+        <v>9.682977606986292</v>
       </c>
       <c r="D2" t="n">
-        <v>24.75967710110456</v>
+        <v>28.42355953335365</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.43093048890212</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C3" t="n">
-        <v>37.23769042208152</v>
+        <v>22.47711368873073</v>
       </c>
       <c r="D3" t="n">
-        <v>69.93970645054277</v>
+        <v>78.64289984869075</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.67859295227957</v>
+        <v>10.29951516525329</v>
       </c>
       <c r="C4" t="n">
-        <v>59.29559784109885</v>
+        <v>66.22575488537709</v>
       </c>
       <c r="D4" t="n">
-        <v>70.57784245830319</v>
+        <v>80.68591682122836</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.80171232593793</v>
+        <v>16.54244881655876</v>
       </c>
       <c r="C5" t="n">
-        <v>78.26983572107697</v>
+        <v>117.3188506574939</v>
       </c>
       <c r="D5" t="n">
-        <v>47.1238898038469</v>
+        <v>52.84257018108458</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.64909946342317</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>75.95487463446298</v>
+        <v>126.8732193152238</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>40.45291415348983</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>53.05953642372311</v>
+        <v>81.98476903394689</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>28.12216298814988</v>
+        <v>37.88564390688441</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26931907438225</v>
+        <v>17.72613558626783</v>
       </c>
       <c r="C21" t="n">
-        <v>76.32785028101362</v>
+        <v>127.6281762211284</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451989305786688</v>
+        <v>5.317840675880348</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.478733026773948</v>
+        <v>1.519745446174062</v>
       </c>
       <c r="C2" t="n">
-        <v>3.379175598017521</v>
+        <v>6.041675371934871</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6099116707113</v>
+        <v>22.58510593619787</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.94143929511046</v>
+        <v>6.454991155422778</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94053966286423</v>
+        <v>38.90175278077987</v>
       </c>
       <c r="D3" t="n">
-        <v>73.5181768325224</v>
+        <v>84.89663272474293</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.12001956629214</v>
+        <v>7.938411936539708</v>
       </c>
       <c r="C4" t="n">
-        <v>78.95018688012</v>
+        <v>99.24291192690157</v>
       </c>
       <c r="D4" t="n">
-        <v>89.78573629189205</v>
+        <v>73.44945449322512</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.37942194439156</v>
+        <v>8.418486563916401</v>
       </c>
       <c r="C5" t="n">
-        <v>95.10680884890976</v>
+        <v>75.79092276785377</v>
       </c>
       <c r="D5" t="n">
-        <v>61.85010536754907</v>
+        <v>39.3680829402971</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94094057349173</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="C6" t="n">
-        <v>102.7222257907523</v>
+        <v>53.97747052719389</v>
       </c>
       <c r="D6" t="n">
-        <v>42.38499363544755</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>84.14068699247288</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>50.98706702005809</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.475017641109688</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.0283256676227</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540640435970977</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
